--- a/tools/importer/reports/import-diagnostics.report.xlsx
+++ b/tools/importer/reports/import-diagnostics.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,13 +61,31 @@
     <t>https://www.beckmancoulter.com/en/blog/diagnostics/modernize-sti-diagnostics-and-surveillance</t>
   </si>
   <si>
+    <t>en/blog/diagnostics/syphilis-unveiling-the-past-and-present-of-a-persistent-disease.report.json</t>
+  </si>
+  <si>
+    <t>["hero-blog","blog-tags","author-bio","cards-blog"]</t>
+  </si>
+  <si>
+    <t>en/blog/diagnostics/syphilis-unveiling-the-past-and-present-of-a-persistent-disease</t>
+  </si>
+  <si>
+    <t>2026-09-10T05:09:36.039Z</t>
+  </si>
+  <si>
+    <t>Syphilis: Unveiling the Past and Present of a Persistent Disease | Beckman Coulter</t>
+  </si>
+  <si>
+    <t>https://www.beckmancoulter.com/en/blog/diagnostics/syphilis-unveiling-the-past-and-present-of-a-persistent-disease</t>
+  </si>
+  <si>
     <t>en/blog/diagnostics/the-value-of-mpv-in-hematology.report.json</t>
   </si>
   <si>
     <t>en/blog/diagnostics/the-value-of-mpv-in-hematology</t>
   </si>
   <si>
-    <t>2026-09-08T07:11:42.315Z</t>
+    <t>2026-09-10T05:11:39.834Z</t>
   </si>
   <si>
     <t>The Value of Mean Platelet Volume (MPV) in Hematology | Beckman Coulter</t>
@@ -462,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -528,10 +546,10 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -540,13 +558,39 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
